--- a/agriculture 11.xlsx
+++ b/agriculture 11.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t xml:space="preserve">2020-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit:- </t>
   </si>
   <si>
     <r>
@@ -287,7 +290,6 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Source</t>
     </r>
@@ -297,7 +299,6 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">: EPWRF (Economic&amp; Political Weekly Research Foundation) (1950-2021)</t>
     </r>
@@ -310,7 +311,6 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Description</t>
     </r>
@@ -320,7 +320,6 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">:  Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
     </r>
@@ -334,7 +333,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -373,11 +372,17 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -436,7 +441,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -466,7 +471,23 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -487,7 +508,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AC1048576"/>
-  <sheetFormatPr defaultColWidth="10.78515625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="43.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -5171,46 +5192,126 @@
       <c r="D60" s="7"/>
       <c r="E60" s="7"/>
       <c r="F60" s="7"/>
-    </row>
-    <row r="61" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="7"/>
-      <c r="B61" s="7"/>
-      <c r="C61" s="7"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="7"/>
+      <c r="G60" s="7"/>
+      <c r="H60" s="7"/>
+      <c r="I60" s="7"/>
+      <c r="J60" s="7"/>
+      <c r="K60" s="7"/>
+      <c r="L60" s="7"/>
+      <c r="M60" s="7"/>
+      <c r="N60" s="7"/>
+      <c r="O60" s="7"/>
+      <c r="P60" s="7"/>
+      <c r="Q60" s="7"/>
+      <c r="R60" s="7"/>
+      <c r="S60" s="7"/>
+      <c r="T60" s="7"/>
+      <c r="U60" s="7"/>
+      <c r="V60" s="7"/>
+      <c r="W60" s="7"/>
+      <c r="X60" s="7"/>
+      <c r="Y60" s="7"/>
+      <c r="Z60" s="7"/>
+      <c r="AA60" s="7"/>
+      <c r="AB60" s="7"/>
+    </row>
+    <row r="61" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B61" s="8"/>
+      <c r="C61" s="8"/>
+      <c r="D61" s="8"/>
+      <c r="E61" s="8"/>
+      <c r="F61" s="8"/>
+      <c r="G61" s="8"/>
+      <c r="H61" s="8"/>
+      <c r="I61" s="8"/>
+      <c r="J61" s="8"/>
+      <c r="K61" s="8"/>
+      <c r="L61" s="8"/>
+      <c r="M61" s="8"/>
+      <c r="N61" s="8"/>
+      <c r="O61" s="8"/>
+      <c r="P61" s="8"/>
+      <c r="Q61" s="8"/>
+      <c r="R61" s="8"/>
+      <c r="S61" s="8"/>
+      <c r="T61" s="8"/>
+      <c r="U61" s="8"/>
+      <c r="V61" s="8"/>
+      <c r="W61" s="8"/>
+      <c r="X61" s="8"/>
+      <c r="Y61" s="8"/>
+      <c r="Z61" s="8"/>
+      <c r="AA61" s="8"/>
+      <c r="AB61" s="8"/>
+    </row>
+    <row r="62" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B62" s="9"/>
+      <c r="C62" s="9"/>
+      <c r="D62" s="9"/>
+      <c r="E62" s="9"/>
+      <c r="F62" s="9"/>
+      <c r="G62" s="9"/>
+      <c r="H62" s="9"/>
+      <c r="I62" s="9"/>
+      <c r="J62" s="9"/>
+      <c r="K62" s="9"/>
+      <c r="L62" s="9"/>
+      <c r="M62" s="9"/>
+      <c r="N62" s="9"/>
+      <c r="O62" s="9"/>
+      <c r="P62" s="9"/>
+      <c r="Q62" s="9"/>
+      <c r="R62" s="9"/>
+      <c r="S62" s="9"/>
+      <c r="T62" s="9"/>
+      <c r="U62" s="9"/>
+      <c r="V62" s="9"/>
+      <c r="W62" s="9"/>
+      <c r="X62" s="9"/>
+      <c r="Y62" s="9"/>
+      <c r="Z62" s="9"/>
+      <c r="AA62" s="9"/>
+      <c r="AB62" s="9"/>
     </row>
     <row r="64" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="B64" s="7"/>
-      <c r="C64" s="7"/>
-      <c r="D64" s="7"/>
-      <c r="E64" s="7"/>
-      <c r="F64" s="7"/>
-    </row>
-    <row r="65" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="7"/>
-      <c r="B65" s="7"/>
-      <c r="C65" s="7"/>
-      <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
-      <c r="F65" s="7"/>
-    </row>
-    <row r="66" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="7"/>
-      <c r="B66" s="7"/>
-      <c r="C66" s="7"/>
-      <c r="D66" s="7"/>
-      <c r="E66" s="7"/>
-      <c r="F66" s="7"/>
+      <c r="A64" s="10"/>
+      <c r="B64" s="10"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="10"/>
+      <c r="E64" s="10"/>
+      <c r="F64" s="10"/>
+    </row>
+    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="10"/>
+      <c r="B65" s="10"/>
+      <c r="C65" s="10"/>
+      <c r="D65" s="10"/>
+      <c r="E65" s="10"/>
+      <c r="F65" s="10"/>
+    </row>
+    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="10"/>
+      <c r="B66" s="10"/>
+      <c r="C66" s="10"/>
+      <c r="D66" s="10"/>
+      <c r="E66" s="10"/>
+      <c r="F66" s="10"/>
+    </row>
+    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C69" s="11"/>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A60:F61"/>
-    <mergeCell ref="A64:F66"/>
+  <mergeCells count="3">
+    <mergeCell ref="A60:AB60"/>
+    <mergeCell ref="A61:AB61"/>
+    <mergeCell ref="A62:AB62"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/agriculture 11.xlsx
+++ b/agriculture 11.xlsx
@@ -280,7 +280,7 @@
     <t xml:space="preserve">2020-21</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- </t>
+    <t xml:space="preserve">Unit:- Percentage (%)</t>
   </si>
   <si>
     <r>
@@ -290,6 +290,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Source</t>
     </r>
@@ -299,6 +300,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">: EPWRF (Economic&amp; Political Weekly Research Foundation) (1950-2021)</t>
     </r>
@@ -311,6 +313,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Description</t>
     </r>
@@ -320,6 +323,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">:  Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
     </r>
@@ -333,7 +337,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -372,17 +376,11 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -441,7 +439,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -474,11 +472,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -486,7 +480,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -508,7 +502,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AC1048576"/>
-  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.8125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="43.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -5216,95 +5210,95 @@
       <c r="AB60" s="7"/>
     </row>
     <row r="61" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="8" t="s">
+      <c r="A61" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="B61" s="8"/>
-      <c r="C61" s="8"/>
-      <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
-      <c r="F61" s="8"/>
-      <c r="G61" s="8"/>
-      <c r="H61" s="8"/>
-      <c r="I61" s="8"/>
-      <c r="J61" s="8"/>
-      <c r="K61" s="8"/>
-      <c r="L61" s="8"/>
-      <c r="M61" s="8"/>
-      <c r="N61" s="8"/>
-      <c r="O61" s="8"/>
-      <c r="P61" s="8"/>
-      <c r="Q61" s="8"/>
-      <c r="R61" s="8"/>
-      <c r="S61" s="8"/>
-      <c r="T61" s="8"/>
-      <c r="U61" s="8"/>
-      <c r="V61" s="8"/>
-      <c r="W61" s="8"/>
-      <c r="X61" s="8"/>
-      <c r="Y61" s="8"/>
-      <c r="Z61" s="8"/>
-      <c r="AA61" s="8"/>
-      <c r="AB61" s="8"/>
+      <c r="B61" s="7"/>
+      <c r="C61" s="7"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="7"/>
+      <c r="G61" s="7"/>
+      <c r="H61" s="7"/>
+      <c r="I61" s="7"/>
+      <c r="J61" s="7"/>
+      <c r="K61" s="7"/>
+      <c r="L61" s="7"/>
+      <c r="M61" s="7"/>
+      <c r="N61" s="7"/>
+      <c r="O61" s="7"/>
+      <c r="P61" s="7"/>
+      <c r="Q61" s="7"/>
+      <c r="R61" s="7"/>
+      <c r="S61" s="7"/>
+      <c r="T61" s="7"/>
+      <c r="U61" s="7"/>
+      <c r="V61" s="7"/>
+      <c r="W61" s="7"/>
+      <c r="X61" s="7"/>
+      <c r="Y61" s="7"/>
+      <c r="Z61" s="7"/>
+      <c r="AA61" s="7"/>
+      <c r="AB61" s="7"/>
     </row>
     <row r="62" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="9" t="s">
+      <c r="A62" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="B62" s="9"/>
-      <c r="C62" s="9"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="9"/>
-      <c r="F62" s="9"/>
-      <c r="G62" s="9"/>
-      <c r="H62" s="9"/>
-      <c r="I62" s="9"/>
-      <c r="J62" s="9"/>
-      <c r="K62" s="9"/>
-      <c r="L62" s="9"/>
-      <c r="M62" s="9"/>
-      <c r="N62" s="9"/>
-      <c r="O62" s="9"/>
-      <c r="P62" s="9"/>
-      <c r="Q62" s="9"/>
-      <c r="R62" s="9"/>
-      <c r="S62" s="9"/>
-      <c r="T62" s="9"/>
-      <c r="U62" s="9"/>
-      <c r="V62" s="9"/>
-      <c r="W62" s="9"/>
-      <c r="X62" s="9"/>
-      <c r="Y62" s="9"/>
-      <c r="Z62" s="9"/>
-      <c r="AA62" s="9"/>
-      <c r="AB62" s="9"/>
+      <c r="B62" s="8"/>
+      <c r="C62" s="8"/>
+      <c r="D62" s="8"/>
+      <c r="E62" s="8"/>
+      <c r="F62" s="8"/>
+      <c r="G62" s="8"/>
+      <c r="H62" s="8"/>
+      <c r="I62" s="8"/>
+      <c r="J62" s="8"/>
+      <c r="K62" s="8"/>
+      <c r="L62" s="8"/>
+      <c r="M62" s="8"/>
+      <c r="N62" s="8"/>
+      <c r="O62" s="8"/>
+      <c r="P62" s="8"/>
+      <c r="Q62" s="8"/>
+      <c r="R62" s="8"/>
+      <c r="S62" s="8"/>
+      <c r="T62" s="8"/>
+      <c r="U62" s="8"/>
+      <c r="V62" s="8"/>
+      <c r="W62" s="8"/>
+      <c r="X62" s="8"/>
+      <c r="Y62" s="8"/>
+      <c r="Z62" s="8"/>
+      <c r="AA62" s="8"/>
+      <c r="AB62" s="8"/>
     </row>
     <row r="64" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="10"/>
-      <c r="B64" s="10"/>
-      <c r="C64" s="10"/>
-      <c r="D64" s="10"/>
-      <c r="E64" s="10"/>
-      <c r="F64" s="10"/>
+      <c r="A64" s="9"/>
+      <c r="B64" s="9"/>
+      <c r="C64" s="9"/>
+      <c r="D64" s="9"/>
+      <c r="E64" s="9"/>
+      <c r="F64" s="9"/>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="10"/>
-      <c r="B65" s="10"/>
-      <c r="C65" s="10"/>
-      <c r="D65" s="10"/>
-      <c r="E65" s="10"/>
-      <c r="F65" s="10"/>
+      <c r="A65" s="9"/>
+      <c r="B65" s="9"/>
+      <c r="C65" s="9"/>
+      <c r="D65" s="9"/>
+      <c r="E65" s="9"/>
+      <c r="F65" s="9"/>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="10"/>
-      <c r="B66" s="10"/>
-      <c r="C66" s="10"/>
-      <c r="D66" s="10"/>
-      <c r="E66" s="10"/>
-      <c r="F66" s="10"/>
+      <c r="A66" s="9"/>
+      <c r="B66" s="9"/>
+      <c r="C66" s="9"/>
+      <c r="D66" s="9"/>
+      <c r="E66" s="9"/>
+      <c r="F66" s="9"/>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C69" s="11"/>
+      <c r="C69" s="10"/>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
